--- a/results/result_evaluation_logs/E_One_Agent_Architecture.xlsx
+++ b/results/result_evaluation_logs/E_One_Agent_Architecture.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,11 +544,6 @@
           <t>Result String</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Langfuse Trace ID</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -564,7 +559,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -573,7 +568,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -582,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -603,7 +598,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -612,7 +607,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -678,11 +673,6 @@
 </t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>614e5a20-3e03-4259-a9d1-5c351f3373b3</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -760,11 +750,6 @@
 </t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0089fbaf-3127-4f3d-9203-768a8f830868</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -840,11 +825,6 @@
 wd:Q466774 wd:P108 wd:Q273626 .
 wd:Q466774 wd:P184 wd:Q370496 .
 </t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>6ee91bfa-9001-4e63-93ca-de2c4475977d</t>
         </is>
       </c>
     </row>
@@ -929,11 +909,6 @@
 </t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>6125be9c-e323-4ace-afe5-92ed125427a8</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1010,11 +985,6 @@
 </t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3c4c7e45-5d3e-44bb-94c5-47103313202d</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1091,11 +1061,6 @@
 </t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>901fe3fa-1bcd-4c42-9589-a80962dd4c35</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1172,11 +1137,6 @@
 </t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>89375336-c468-412f-bab0-9a8251465fad</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1192,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1201,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1210,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1231,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1240,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1306,11 +1266,6 @@
 </t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5b20e9ea-fb11-4dbc-99f4-fd8675e35c07</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1392,11 +1347,6 @@
 </t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7e1e8eb0-2e65-47a6-a055-0b2e639ac263</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1476,11 +1426,6 @@
 </t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>113cf1ca-55a3-4a5b-8199-9363df3b485f</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1558,11 +1503,6 @@
 </t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>78f1d3b9-5583-4435-9acf-ac584585f513</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1637,11 +1577,6 @@
 &lt;http://www.wikidata.org/entity/Q271108&gt; &lt;http://www.wikidata.org/entity/P1344&gt; &lt;http://www.wikidata.org/entity/Q516760&gt; .
 &lt;http://www.wikidata.org/entity/Q516760&gt; &lt;http://www.wikidata.org/entity/P276&gt; &lt;http://www.wikidata.org/entity/Q1605654&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>3edf1112-5c56-499c-8fd7-d08ae25592fa</t>
         </is>
       </c>
     </row>
@@ -1721,11 +1656,6 @@
 </t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6bcee76a-cee9-4516-af8f-42894d6645da</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1741,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1750,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1759,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1780,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1789,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1855,11 +1785,6 @@
 </t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>144435f6-d0fb-410a-8182-5d2f48b19ade</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1936,11 +1861,6 @@
 </t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>ece67166-ffb0-4147-8add-6a0c4e6cee02</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1956,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1965,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1974,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1995,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -2004,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2070,11 +1990,6 @@
 </t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>a6d75453-4df3-4b6c-a7ea-82e862621be4</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2151,11 +2066,6 @@
 wd:Q607380 wd:P5588 wd:Q782 .
 wd:Q607380 wd:P1056 wd:Q6933370 .
 </t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>20dc2293-6e60-4320-adab-9ae963f4683e</t>
         </is>
       </c>
     </row>
@@ -2237,11 +2147,6 @@
 </t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>db2ef380-10ae-4b40-9a38-e9f73f6ce111</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2316,11 +2221,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q20671544 wd:P31 wd:Q27914 .
 </t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>9962d05c-20c3-4887-9f07-5cad4946451e</t>
         </is>
       </c>
     </row>
@@ -2403,11 +2303,6 @@
 </t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>23e48f80-a941-49cf-ad0d-d4e047be9e7b</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2482,11 +2377,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q17052475 wd:P279 wd:Q11348 .
 </t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>98c5cd14-2dbd-4f3a-9ecc-8717cd5ab27a</t>
         </is>
       </c>
     </row>
@@ -2567,11 +2457,6 @@
 </t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>bb46cc4b-49f3-4629-b5bd-96bb3b92b5b1</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2647,11 +2532,6 @@
 wd:Q188197 wd:P2522 wd:Q1856183 .
 wd:Q188197 wd:P2522 wd:Q674962 .
 </t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>240a1579-f14c-4b71-8315-220a153debd6</t>
         </is>
       </c>
     </row>
@@ -2730,11 +2610,6 @@
 wd:Q5554167 wd:P750 wd:Q520445 .
 wd:Q5554167 wd:P449 wd:Q220072 .
 </t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>d932b914-b8ae-443a-a693-8e376c44d462</t>
         </is>
       </c>
     </row>
@@ -2818,11 +2693,6 @@
 </t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>d83e4219-656d-406e-a9a8-12996fa023e7</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2900,11 +2770,6 @@
 </t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>30ca4a50-83bd-4ec4-8c6e-3aa2090cc876</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2980,11 +2845,6 @@
 wd:Q22082365 wd:P131 wd:Q965 .
 wd:Q965 wd:P463 wd:Q47543 .
 </t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>7ff73db3-3181-4045-a029-0b97bdad45fd</t>
         </is>
       </c>
     </row>
@@ -3065,11 +2925,6 @@
 </t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>bf030a70-876a-4a64-b20a-13ae9b6aa193</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3085,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -3094,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -3103,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3124,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -3133,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -3199,11 +3054,6 @@
 </t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>e799b293-5a1e-4c50-8990-19081120c89b</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3282,11 +3132,6 @@
 </t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>9a1bbc96-f13c-41df-b284-7b1ee6fa591e</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3332,10 +3177,10 @@
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>2</v>
@@ -3362,11 +3207,6 @@
 wd:Q64876878 wd:P161 wd:Q65090308 .
 wd:Q64876878 wd:P725 wd:Q262170 .
 </t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>4032b3c0-d877-49cc-b3af-4da41c03bd82</t>
         </is>
       </c>
     </row>
@@ -3448,11 +3288,6 @@
 </t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>3e0145f1-3fe8-449c-a676-4262d9cb841f</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3531,11 +3366,6 @@
 </t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>17766ac1-98ad-44d5-8eff-ea51152ece4e</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3612,11 +3442,6 @@
 </t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>e1488d81-c951-4d7d-bc38-1e99fbb66cb6</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3691,11 +3516,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q1490434 wd:P31 wd:Q41298 .
 </t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>52df7de0-d4c5-43cf-912a-bc64702289e1</t>
         </is>
       </c>
     </row>
@@ -3774,11 +3594,6 @@
 wd:Q2616869 wd:P1433 wd:Q1126800 .
 wd:Q2616869 wd:P6216 wd:Q19652 .
 </t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>1ce83033-4867-4cf2-b9c2-ab55a0379292</t>
         </is>
       </c>
     </row>
@@ -3863,11 +3678,6 @@
 </t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>28b5b672-4752-4d64-ad2c-a505a170c3b0</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3945,11 +3755,6 @@
 </t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>3472be6a-7171-4c50-ab3f-83e96d5faa8a</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4024,11 +3829,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q1064344 wd:P361 wd:Q1406 .
 </t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>efc05dd4-37a8-482f-9768-9a99b778e8eb</t>
         </is>
       </c>
     </row>
@@ -4106,11 +3906,6 @@
 wd:Q47554 wd:P1376 wd:Q54153 .
 wd:Q47554 wd:P706 wd:Q1261531 .
 </t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>1999f101-526e-4db7-acf2-79061a8786e1</t>
         </is>
       </c>
     </row>
@@ -4196,11 +3991,6 @@
 </t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>fcbd25b8-5e20-4850-96d8-4ddfbf50259e</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4278,11 +4068,6 @@
 </t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>83ae89de-655f-475c-8e84-d10c9d550aad</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4298,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -4307,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4316,7 +4101,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -4337,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -4346,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -4412,11 +4197,6 @@
 </t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>06e1780e-1de3-44c3-90b6-014493bc4885</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4497,11 +4277,6 @@
 </t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>9306be7c-8bec-471f-b007-24a316aca270</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4580,11 +4355,6 @@
 </t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>ab19f71e-3207-41fa-b969-61a4126fa4c8</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4659,11 +4429,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q18036732 wd:P276 wd:Q753805 .
 </t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>62a5fc14-3958-4af4-9930-dd3d99340bbf</t>
         </is>
       </c>
     </row>
@@ -4742,11 +4507,6 @@
 wd:Q977911 wd:P361 wd:Q112686 .
 wd:Q979352 wd:P361 wd:Q112686 .
 </t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>478ad14f-efe2-4475-a647-ddf272338502</t>
         </is>
       </c>
     </row>
@@ -4828,11 +4588,6 @@
 </t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>130b7a72-4fec-4932-8da6-1e4b565e48de</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4911,11 +4666,6 @@
 </t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>7f34aced-a949-4b26-b5bd-e832f88da4fe</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4990,11 +4740,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q2362697 wd:P556 wd:Q503601 .
 </t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>badc7d9b-3d84-41f5-bda4-7d5edb1e4b8a</t>
         </is>
       </c>
     </row>
